--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22757-2026 artfynd.xlsx
+++ b/artfynd/A 22757-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136747835</v>
       </c>
       <c r="B2" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136748031</v>
       </c>
       <c r="B3" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136748744</v>
       </c>
       <c r="B4" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136749216</v>
       </c>
       <c r="B5" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
